--- a/PIT_Reform_Optimization_Engine_2/PIT_slabs_2026.xlsx
+++ b/PIT_Reform_Optimization_Engine_2/PIT_slabs_2026.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="47.86328125" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -535,1008 +535,1002 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>600000</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" t="n">
         <v>600001</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" t="n">
         <v>1200000</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" t="n">
         <v>0.05</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>5% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="n">
         <v>1200001</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" t="n">
         <v>2200000</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" t="n">
         <v>0.15</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Rs. 30,000 + 15% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" t="n">
         <v>2200001</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" t="n">
         <v>3200000</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Rs. 180,000 + 25% of the amount exceeding Rs. 2,200,000</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="A6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" t="n">
         <v>3200001</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" t="n">
         <v>4100000</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Rs. 430,000 + 30% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>4100000</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" t="n">
         <v>0.35</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Rs. 700,000 + 35% of the amount exceeding Rs. 4,100,000</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
+      <c r="E8" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>for 10,000,000 10% of the tax liability</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>600000</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" t="n">
         <v>600001</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" t="n">
         <v>1200000</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" t="n">
         <v>0.15</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>15% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" t="n">
         <v>1200001</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" t="n">
         <v>1600000</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" t="n">
         <v>0.2</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" t="n">
         <v>1600001</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" t="n">
         <v>3200000</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" t="n">
         <v>0.3</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="A13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" t="n">
         <v>3200001</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" t="n">
         <v>5600000</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" t="n">
         <v>0.4</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="A14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" t="n">
         <v>5600001</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" t="n">
         <v>0.45</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="A15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n">
+      <c r="E15" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>for 10,000,000 10% of the tax liability</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="A16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>600000</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" t="n">
         <v>600001</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" t="n">
         <v>1200000</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" t="n">
         <v>0.15</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>15% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" t="n">
         <v>1200001</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" t="n">
         <v>1600000</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" t="n">
         <v>0.2</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="A19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" t="n">
         <v>1600001</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" t="n">
         <v>3200000</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" t="n">
         <v>0.3</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" t="n">
         <v>3200001</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" t="n">
         <v>5600000</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" t="n">
         <v>0.4</v>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" t="n">
         <v>5600001</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" t="n">
         <v>0.45</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="A22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n">
+      <c r="E22" t="n">
         <v>0.1</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>for 10,000,000 10% of the tax liability</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="A23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>15% of the amount exceeding Rs. 600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1200001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1600001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3200001</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5600001</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>for 10,000,000 10% of the tax liability</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
         <v>600000</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C31" t="n">
         <v>600001</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D31" t="n">
         <v>1200000</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E31" t="n">
         <v>0.01</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>1% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C32" t="n">
         <v>1200001</v>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D32" t="n">
         <v>2200000</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E32" t="n">
         <v>0.11</v>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Rs. 6,000 + 11% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C33" t="n">
         <v>2200001</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D33" t="n">
         <v>3200000</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E33" t="n">
         <v>0.23</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Rs. 116,000 + 23% of the amount exceeding Rs. 2,200,000</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C34" t="n">
         <v>3200001</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D34" t="n">
         <v>4100000</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E34" t="n">
         <v>0.3</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Rs. 346,000 + 30% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C35" t="n">
         <v>4100000</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E35" t="n">
         <v>0.35</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Rs. 616,000 + 35% of the amount exceeding Rs. 4,100,000</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>salaried</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n">
+      <c r="E36" t="n">
         <v>0.09</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>for 10,000,000 9% of the tax liability</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
         <v>600000</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C38" t="n">
         <v>600001</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D38" t="n">
         <v>1200000</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E38" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>15% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C39" t="n">
         <v>1200001</v>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D39" t="n">
         <v>1600000</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E39" t="n">
         <v>0.2</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C40" t="n">
         <v>1600001</v>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D40" t="n">
         <v>3200000</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E40" t="n">
         <v>0.3</v>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C41" t="n">
         <v>3200001</v>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D41" t="n">
         <v>5600000</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E41" t="n">
         <v>0.4</v>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C42" t="n">
         <v>5600001</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E42" t="n">
         <v>0.45</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Non_salaried</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="1" t="n">
+      <c r="E43" t="n">
         <v>0.1</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>for 10,000,000 10% of the tax liability</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>600000</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>600001</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>15% of the amount exceeding Rs. 600,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1200001</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>1600001</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>3200001</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>5600001</v>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>AOP</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>Surcharge</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>for 10,000,000 10% of the tax liability</t>
         </is>
@@ -1544,11 +1538,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1566,11 +1560,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1580,298 +1574,299 @@
         <v>1200000</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1% of the amount exceeding Rs. 600,000</t>
+          <t>15% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1200001</v>
       </c>
       <c r="D46" t="n">
-        <v>2200000</v>
+        <v>1600000</v>
       </c>
       <c r="E46" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rs. 6,000 + 11% of the amount exceeding Rs. 1,200,000</t>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2200001</v>
+        <v>1600001</v>
       </c>
       <c r="D47" t="n">
         <v>3200000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rs. 116,000 + 20% of the amount exceeding Rs. 2,200,000</t>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>3200001</v>
       </c>
       <c r="D48" t="n">
-        <v>4100000</v>
+        <v>5600000</v>
       </c>
       <c r="E48" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rs. 316,000 + 25% of the amount exceeding Rs. 3,200,000</t>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>AOP</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4100001</v>
-      </c>
-      <c r="D49" t="n">
-        <v>5600000</v>
+        <v>5600001</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rs. 541,000 + 29% of the amount exceeding Rs. 4,100,000</t>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>salaried</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5600001</v>
-      </c>
-      <c r="D50" t="n">
-        <v>7000000</v>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
       </c>
       <c r="E50" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rs. 976,000 + 32% of the amount exceeding Rs. 5,600,000</t>
+          <t>for 10,000,000 10% of the tax liability</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>salaried</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7000001</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>600000</v>
       </c>
       <c r="E51" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Rs. 1,424,000 + 35% of the amount exceeding Rs. 7,000,000</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>salaried</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Surcharge</t>
-        </is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1200000</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nil - abolished for salaried individuals by Finance Act 2026</t>
+          <t>15% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1200001</v>
       </c>
       <c r="D53" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>600001</v>
+        <v>1600001</v>
       </c>
       <c r="D54" t="n">
-        <v>1200000</v>
+        <v>3200000</v>
       </c>
       <c r="E54" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>15% of the amount exceeding Rs. 600,000</t>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1200001</v>
+        <v>3200001</v>
       </c>
       <c r="D55" t="n">
-        <v>1600000</v>
+        <v>5600000</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1600001</v>
-      </c>
-      <c r="D56" t="n">
-        <v>3200000</v>
+        <v>5600001</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
       </c>
       <c r="E56" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>3200001</v>
-      </c>
-      <c r="D57" t="n">
-        <v>5600000</v>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
       </c>
       <c r="E57" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+          <t>for 10,000,000 10% of the tax liability</t>
         </is>
       </c>
     </row>
@@ -1881,24 +1876,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5600001</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>600000</v>
       </c>
       <c r="E58" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1907,20 +1898,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Non_salaried</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Surcharge</t>
-        </is>
+          <t>salaried</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1200000</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>for 10,000,000 10% of the tax liability</t>
+          <t>1% of the amount exceeding Rs. 600,000</t>
         </is>
       </c>
     </row>
@@ -1930,20 +1922,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1200001</v>
       </c>
       <c r="D60" t="n">
-        <v>600000</v>
+        <v>2200000</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rs. 6,000 + 11% of the amount exceeding Rs. 1,200,000</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1952,21 +1946,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>600001</v>
+        <v>2200001</v>
       </c>
       <c r="D61" t="n">
-        <v>1200000</v>
+        <v>3200000</v>
       </c>
       <c r="E61" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>15% of the amount exceeding Rs. 600,000</t>
+          <t>Rs. 116,000 + 20% of the amount exceeding Rs. 2,200,000</t>
         </is>
       </c>
     </row>
@@ -1976,21 +1970,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1200001</v>
+        <v>3200001</v>
       </c>
       <c r="D62" t="n">
-        <v>1600000</v>
+        <v>4100000</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+          <t>Rs. 316,000 + 25% of the amount exceeding Rs. 3,200,000</t>
         </is>
       </c>
     </row>
@@ -2000,21 +1994,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1600001</v>
+        <v>4100001</v>
       </c>
       <c r="D63" t="n">
-        <v>3200000</v>
+        <v>5600000</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+          <t>Rs. 541,000 + 29% of the amount exceeding Rs. 4,100,000</t>
         </is>
       </c>
     </row>
@@ -2024,21 +2018,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3200001</v>
+        <v>5600001</v>
       </c>
       <c r="D64" t="n">
-        <v>5600000</v>
+        <v>7000000</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+          <t>Rs. 976,000 + 32% of the amount exceeding Rs. 5,600,000</t>
         </is>
       </c>
     </row>
@@ -2048,11 +2042,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AOP</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5600001</v>
+        <v>7000001</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2060,11 +2054,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
+          <t>Rs. 1,424,000 + 35% of the amount exceeding Rs. 7,000,000</t>
         </is>
       </c>
     </row>
@@ -2074,18 +2068,519 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>salaried</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nil - abolished for salaried individuals by Finance Act 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>15% of the amount exceeding Rs. 600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1200001</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1600001</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3200001</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>5600001</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Non_salaried</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>for 10,000,000 10% of the tax liability</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>15% of the amount exceeding Rs. 600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1200001</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1600001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3200001</v>
+      </c>
+      <c r="D78" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>5600001</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>Surcharge</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E80" t="n">
         <v>0.1</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>for 10,000,000 10% of the tax liability</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>600001</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>15% of the amount exceeding Rs. 600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1200001</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Rs. 90,000 + 20% of the amount exceeding Rs. 1,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1600001</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Rs. 170,000 + 30% of the amount exceeding Rs. 1,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3200001</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Rs. 650,000 + 40% of the amount exceeding Rs. 3,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5600001</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rs. 1,610,000 + 45% of the amount exceeding Rs. 5,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Surcharge</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>for 10,000,000 10% of the tax liability</t>
         </is>
@@ -2102,7 +2597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2129,7 +2624,7 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Non-salaried / AOP surcharge (&gt;Rs 10M)</t>
+          <t>Non-salaried / AOP / NSC surcharge (&gt;Rs 10M)</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2688,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
@@ -2212,6 +2706,13 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>Changes vs PIT_slabs_2025.xlsx: 2026 salaried surcharge 10% -&gt; 9%; 2026 salaried text fixes (345,000 -&gt; 346,000; "1" -&gt; "1% of..."); 2027 rows added. 2025 and 2026 MTRs unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NSC = Non-Salaried + AOP combined (as in the observations data). NSC rows copy the Non_salaried schedule in every year, since NS and AOP are taxed on the same schedule.</t>
         </is>
       </c>
     </row>
